--- a/CBT_2021_3회/산업안전기사_2021_3회_문항등록.xlsx
+++ b/CBT_2021_3회/산업안전기사_2021_3회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="AH4" s="32" t="inlineStr">
         <is>
-          <t>① 20% 는 기준값이 아니다.&lt;br&gt;③ 40% 도 그렇다.&lt;br&gt;④ 50% 도 그렇다.</t>
+          <t>① 20%는 기준값이 아니다.&lt;br&gt;③ 40% 도 그렇다.&lt;br&gt;④ 50% 도 그렇다.</t>
         </is>
       </c>
       <c r="AI4" s="32" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AG8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내전압성시험과 내수성시험&lt;/strong&gt;이다. &lt;strong&gt;E 가 붙은 것만 전기용&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 종류와 시험항목&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;시험항목&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 및 추락 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;내관통성 · 충격흡수성 · 난연성 · 턱끈풀림&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 및 감전 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;위 항목 + &lt;u&gt;내전압성 · 내수성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ABE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 · 추락 · 감전 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 항목&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내전압성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교류 20kV 에서 1분간 견디고 누설전류 10mA 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질량증가율 1% 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;내전압성시험과 내수성시험&lt;/strong&gt;이다. &lt;strong&gt;E가 붙은 것만 전기용&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 종류와 시험항목&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;시험항목&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 및 추락 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;내관통성 · 충격흡수성 · 난연성 · 턱끈풀림&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 및 감전 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;위 항목 + &lt;u&gt;내전압성 · 내수성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ABE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 · 추락 · 감전 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모든 항목&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내전압성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교류 20kV에서 1분간 견디고 누설전류 10mA 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;질량증가율 1% 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH8" s="32" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="AI8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전모의 성능시험&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「E」는 Electric — 전기&lt;/strong&gt;다 — &lt;strong&gt;E 가 붙은 AE · ABE 만 전기에 관한 시험(내전압성 · 내수성)&lt;/strong&gt;을 더한다. &lt;strong&gt;젖으면 전기가 통하니 내수성도 함께&lt;/strong&gt; 본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AE·ABE 만 내전압성·내수성 시험&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전모의 성능시험&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「E」는 Electric — 전기&lt;/strong&gt;다 — &lt;strong&gt;E가 붙은 AE · ABE 만 전기에 관한 시험(내전압성 · 내수성)&lt;/strong&gt;을 더한다. &lt;strong&gt;젖으면 전기가 통하니 내수성도 함께&lt;/strong&gt; 본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AE·ABE 만 내전압성·내수성 시험&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2366,17 +2366,17 @@
       </c>
       <c r="AG10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;E 는 환경(Environment)&lt;/strong&gt;이다. &lt;strong&gt;작업환경 · 인간관계 · 설비 같은 둘레의 조건&lt;/strong&gt;을 말한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈(Lewin)의 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior — 인간의 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function — 함수관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person — 사람의 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연령 · 성격 · 지능 · 소질 · 경험 · 심신 상태&lt;/u&gt; · ①②④&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment — 환경 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업환경 · 인간관계 · 설비적 결함&lt;/u&gt; · ③&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;E는 환경(Environment)&lt;/strong&gt;이다. &lt;strong&gt;작업환경 · 인간관계 · 설비 같은 둘레의 조건&lt;/strong&gt;을 말한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈(Lewin)의 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior — 인간의 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function — 함수관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person — 사람의 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연령 · 성격 · 지능 · 소질 · 경험 · 심신 상태&lt;/u&gt; · ①②④&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment — 환경 조건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업환경 · 인간관계 · 설비적 결함&lt;/u&gt; · ③&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH10" s="32" t="inlineStr">
         <is>
-          <t>① 연령은 P 에 드는 조건이다.&lt;br&gt;② 성격도 그렇다.&lt;br&gt;④ 지능도 그렇다.</t>
+          <t>① 연령은 P에 드는 조건이다.&lt;br&gt;② 성격도 그렇다.&lt;br&gt;④ 지능도 그렇다.</t>
         </is>
       </c>
       <c r="AI10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 셋이 모두 사람의 속성(P)&lt;/strong&gt;이고 &lt;strong&gt;하나만 둘레의 조건(E)&lt;/strong&gt;이다 — &lt;strong&gt;「환경」이라는 낱말이 들어간 것&lt;/strong&gt;을 고르면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;B = f(P · E), E 는 환경&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 셋이 모두 사람의 속성(P)&lt;/strong&gt;이고 &lt;strong&gt;하나만 둘레의 조건(E)&lt;/strong&gt;이다 — &lt;strong&gt;「환경」이라는 낱말이 들어간 것&lt;/strong&gt;을 고르면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;B = f(P · E), E는 환경&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AH17" s="32" t="inlineStr">
         <is>
-          <t>① 2 는 계산과 맞지 않는다.&lt;br&gt;② 5 는 재해 건수를 그대로 쓴 값이다.&lt;br&gt;④ 20 도 그렇다.</t>
+          <t>① 2는 계산과 맞지 않는다.&lt;br&gt;② 5는 재해 건수를 그대로 쓴 값이다.&lt;br&gt;④ 20 도 그렇다.</t>
         </is>
       </c>
       <c r="AI17" s="32" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AH19" s="32" t="inlineStr">
         <is>
-          <t>① 7.32 는 휴업일수를 환산하지 않은 값에 가깝다.&lt;br&gt;③ 8.12 는 계산과 맞지 않는다.&lt;br&gt;④ 5.92 도 그렇다.</t>
+          <t>① 7.32는 휴업일수를 환산하지 않은 값에 가깝다.&lt;br&gt;③ 8.12는 계산과 맞지 않는다.&lt;br&gt;④ 5.92 도 그렇다.</t>
         </is>
       </c>
       <c r="AI19" s="32" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AI22" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재해코스트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「보험에서 나오는 돈이면 직접비, 회사가 따로 무는 돈이면 간접비」&lt;/strong&gt;다 — &lt;strong&gt;설비를 고치는 값은 보험이 주지 않는다&lt;/strong&gt;. &lt;strong&gt;1 : 4 라는 비율&lt;/strong&gt;도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직접비 : 간접비 = 1 : 4&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;재해코스트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「보험에서 나오는 돈이면 직접비, 회사가 따로 무는 돈이면 간접비」&lt;/strong&gt;다 — &lt;strong&gt;설비를 고치는 값은 보험이 주지 않는다&lt;/strong&gt;. &lt;strong&gt;1 : 4라는 비율&lt;/strong&gt;도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;직접비 : 간접비 = 1 : 4&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       <c r="AA24" s="32" t="inlineStr"/>
       <c r="AB24" s="32" t="inlineStr">
         <is>
-          <t>「그것이 발생하기 위해서는 무엇이 필요한가」 라는 것은 연역적이다.</t>
+          <t>「그것이 발생하기 위해서는 무엇이 필요한가」라는 것은 연역적이다.</t>
         </is>
       </c>
       <c r="AC24" s="32" t="inlineStr"/>
@@ -4172,17 +4172,17 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「그것이 일어나려면 무엇이 있어야 하나」를 거슬러 올라가는 연역적 방법&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 성격&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상에서 원인으로 내려간다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연역적(top-down)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;성격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적·정량적 분석이 모두 된다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;적용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;복잡하고 대형화된 시스템에 알맞다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①이 틀린 까닭&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FMEA 와의 차이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FMEA 는 귀납적·상향식(bottom-up)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②④는 ETA·FMEA 쪽 설명&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「그것이 일어나려면 무엇이 있어야 하나」를 거슬러 올라가는 연역적 방법&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 성격&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상에서 원인으로 내려간다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연역적(top-down)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;성격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적·정량적 분석이 모두 된다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;적용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;복잡하고 대형화된 시스템에 알맞다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①이 틀린 까닭&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FMEA 와의 차이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FMEA는 귀납적·상향식(bottom-up)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②④는 ETA·FMEA 쪽 설명&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>① FTA 는 오히려 복잡하고 큰 시스템에 알맞다.&lt;br&gt;② 구성요소를 정상·고장으로 점진적으로 나누는 것은 FMEA 의 방식이다.&lt;br&gt;④ 이분 의사결정 분기로 모형화하는 것은 ETA 다.</t>
+          <t>① FTA는 오히려 복잡하고 큰 시스템에 알맞다.&lt;br&gt;② 구성요소를 정상·고장으로 점진적으로 나누는 것은 FMEA의 방식이다.&lt;br&gt;④ 이분 의사결정 분기로 모형화하는 것은 ETA다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 특징&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「무엇이 필요한가」를 거꾸로 캐물으면 연역&lt;/strong&gt;이고, &lt;strong&gt;「이것이 고장 나면 어떻게 되나」를 쌓아 올리면 귀납&lt;/strong&gt;이다 — &lt;strong&gt;FTA 가 앞, FMEA 가 뒤&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA 는 연역적, FMEA 는 귀납적&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 특징&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「무엇이 필요한가」를 거꾸로 캐물으면 연역&lt;/strong&gt;이고, &lt;strong&gt;「이것이 고장 나면 어떻게 되나」를 쌓아 올리면 귀납&lt;/strong&gt;이다 — &lt;strong&gt;FTA가 앞, FMEA가 뒤&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FTA는 연역적, FMEA는 귀납적&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;억제 게이트&lt;/strong&gt;다. &lt;strong&gt;조건이 만족될 때만&lt;/strong&gt; 입력이 출력으로 넘어간다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건부 사건이 일어났을 때만 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 육각형 안에 조건을 적는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 모두 일어나야 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 중 하나만 일어나도 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 중 하나만 일어날 때 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 순서로 일어날 때 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;억제 게이트&lt;/strong&gt;다. &lt;strong&gt;조건이 만족될 때만&lt;/strong&gt; 입력이 출력으로 넘어간다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건부 사건이 일어났을 때만 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 육각형 안에 조건을 적는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 모두 일어나야 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 중 하나만 일어나도 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 중 하나만 일어날 때 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 순서로 일어날 때 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
@@ -4426,17 +4426,17 @@
       </c>
       <c r="AG26" s="32" t="inlineStr">
         <is>
-          <t>구간마다 &lt;strong&gt;log(S/N) 에 가중치를 곱해 모두 더한다&lt;/strong&gt;.$AI = (-0.7 \times 1 ) + ( 0.18 \times 1 ) + ( 0.6 \times 2 ) + ( 0.7 \times 1 ) = 1.38$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;명료도 지수(AI)의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;log(S/N)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가중치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;곱&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Ⅰ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−0.7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−0.7&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Ⅱ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.18&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.18&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Ⅲ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.2&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Ⅳ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.7&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.38&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>구간마다 &lt;strong&gt;log(S/N)에 가중치를 곱해 모두 더한다&lt;/strong&gt;.$AI = (-0.7 \times 1 ) + ( 0.18 \times 1 ) + ( 0.6 \times 2 ) + ( 0.7 \times 1 ) = 1.38$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;명료도 지수(AI)의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;log(S/N)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가중치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;곱&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Ⅰ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−0.7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−0.7&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Ⅱ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.18&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.18&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Ⅲ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.2&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Ⅳ&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.7&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.38&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH26" s="32" t="inlineStr">
         <is>
-          <t>① 0.38 은 Ⅲ구간의 가중치를 1 로 잡은 값이다.&lt;br&gt;② 0.68 은 계산과 맞지 않는다.&lt;br&gt;④ 5.68 도 그렇다.</t>
+          <t>① 0.38은 Ⅲ구간의 가중치를 1로 잡은 값이다.&lt;br&gt;② 0.68은 계산과 맞지 않는다.&lt;br&gt;④ 5.68 도 그렇다.</t>
         </is>
       </c>
       <c r="AI26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;명료도 지수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Ⅲ구간의 가중치만 2&lt;/strong&gt;라는 것이 이 문제의 전부다 — &lt;strong&gt;그것을 1 로 보면 0.78, 음수를 빠뜨리면 더 커진다&lt;/strong&gt;. &lt;strong&gt;음수 −0.7 을 빼먹지 않는 것&lt;/strong&gt;이 또 하나의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AI = Σ(log(S/N) × 가중치)&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;명료도 지수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;Ⅲ구간의 가중치만 2&lt;/strong&gt;라는 것이 이 문제의 전부다 — &lt;strong&gt;그것을 1로 보면 0.78, 음수를 빠뜨리면 더 커진다&lt;/strong&gt;. &lt;strong&gt;음수 −0.7을 빼먹지 않는 것&lt;/strong&gt;이 또 하나의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AI = Σ(log(S/N) × 가중치)&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4681,12 +4681,12 @@
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
-          <t>② 수평 계수는 RWL 의 계수다.&lt;br&gt;③ 수직 계수도 그렇다.&lt;br&gt;④ 비대칭 계수도 그렇다.</t>
+          <t>② 수평 계수는 RWL의 계수다.&lt;br&gt;③ 수직 계수도 그렇다.&lt;br&gt;④ 비대칭 계수도 그렇다.</t>
         </is>
       </c>
       <c r="AI28" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;권장무게한계(RWL)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;RWL = LC × HM × VM × DM × AM × FM × CM&lt;/strong&gt;이다 — &lt;strong&gt;부하상수 23kg 에 여섯 계수를 곱한다&lt;/strong&gt;. &lt;strong&gt;「휴식」은 그 목록에 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;RWL 은 LC·HM·VM·DM·AM·FM·CM&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;권장무게한계(RWL)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;RWL = LC × HM × VM × DM × AM × FM × CM&lt;/strong&gt;이다 — &lt;strong&gt;부하상수 23kg에 여섯 계수를 곱한다&lt;/strong&gt;. &lt;strong&gt;「휴식」은 그 목록에 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;RWL은 LC·HM·VM·DM·AM·FM·CM&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>안전장치는 &lt;strong&gt;필요할 때 제대로 작동하는 것&lt;/strong&gt;으로 본다. &lt;strong&gt;「동작하지 않는」이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;HAZOP 의 전제조건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;두 개 이상의 기기고장이나 사고는 동시에 일어나지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;장치와 설비는 설계·제작 사양에 맞게 만들어진 것으로 본다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전장치는 필요할 때 정상 동작하는 것으로 본다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 뒤집혔다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업자는 위험상황이 생기면 알아차릴 수 있다고 본다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사소한 지엽적인 변화도 부작용을 일으킬 수 있다고 본다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>안전장치는 &lt;strong&gt;필요할 때 제대로 작동하는 것&lt;/strong&gt;으로 본다. &lt;strong&gt;「동작하지 않는」이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;HAZOP의 전제조건&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;두 개 이상의 기기고장이나 사고는 동시에 일어나지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;장치와 설비는 설계·제작 사양에 맞게 만들어진 것으로 본다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전장치는 필요할 때 정상 동작하는 것으로 본다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③이 뒤집혔다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업자는 위험상황이 생기면 알아차릴 수 있다고 본다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사소한 지엽적인 변화도 부작용을 일으킬 수 있다고 본다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;HAZOP 의 전제조건&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;HAZOP 은 「설비는 제대로 만들어졌고 안전장치도 잘 듣는다」고 놓고 시작&lt;/strong&gt; 한다 — &lt;strong&gt;그래야 「그런데도 왜 위험한가」&lt;/strong&gt;를 따질 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전장치는 정상 동작하는 것으로 본다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;HAZOP의 전제조건&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;HAZOP은 「설비는 제대로 만들어졌고 안전장치도 잘 듣는다」고 놓고 시작&lt;/strong&gt;한다 — &lt;strong&gt;그래야 「그런데도 왜 위험한가」&lt;/strong&gt;를 따질 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전장치는 정상 동작하는 것으로 본다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① SHA 는 서브시스템 위험분석이다.&lt;br&gt;② FMEA 는 설계 이후 고장형태를 분석하는 기법이다.&lt;br&gt;④ MORT 는 관리 전반을 다루는 프로그램이다.</t>
+          <t>① SHA는 서브시스템 위험분석이다.&lt;br&gt;② FMEA는 설계 이후 고장형태를 분석하는 기법이다.&lt;br&gt;④ MORT는 관리 전반을 다루는 프로그램이다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;예비위험분석(PHA)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「Preliminary(예비)」가 곧 「초기 단계」&lt;/strong&gt;다 — &lt;strong&gt;네 위험등급(파국적 · 중대 · 한계적 · 무시가능)&lt;/strong&gt;으로 나누는 것도 PHA 다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;설계 초기의 위험분석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;예비위험분석(PHA)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「Preliminary(예비)」가 곧 「초기 단계」&lt;/strong&gt;다 — &lt;strong&gt;네 위험등급(파국적 · 중대 · 한계적 · 무시가능)&lt;/strong&gt;으로 나누는 것도 PHA다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;설계 초기의 위험분석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="U36" s="32" t="inlineStr">
         <is>
-          <t>다음 중 신체의 열교환과정을 나타내는 공식으로 올바른 것은? (단, △S 는 신체열함량변화, M 은 대사열발생량, W 는 수행한 일, R 는 복사열교환량, C 는 대류열교환량, E 는 증발열발산량을 의미한다.)</t>
+          <t>다음 중 신체의 열교환과정을 나타내는 공식으로 올바른 것은? (단, △S는 신체열함량변화, M은 대사열발생량, W는 수행한 일, R는 복사열교환량, C는 대류열교환량, E는 증발열발산량을 의미한다.)</t>
         </is>
       </c>
       <c r="V36" s="32" t="inlineStr"/>
@@ -5705,12 +5705,12 @@
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>② W 를 더하면 일한 몫만큼 몸이 더워진다는 뜻이 되어 틀리다.&lt;br&gt;③ E 를 ± 로 두면 증발로 열을 얻을 수도 있다는 뜻이 된다.&lt;br&gt;④ R 와 C 를 − 로만 두면 더운 곳에서 열을 받는 경우를 담지 못한다.</t>
+          <t>② W를 더하면 일한 몫만큼 몸이 더워진다는 뜻이 되어 틀리다.&lt;br&gt;③ E를 ± 로 두면 증발로 열을 얻을 수도 있다는 뜻이 된다.&lt;br&gt;④ R와 C를 − 로만 두면 더운 곳에서 열을 받는 경우를 담지 못한다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;신체의 열교환&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「W 는 빼기, E 도 빼기, R 와 C 만 ±」&lt;/strong&gt;다 — &lt;strong&gt;땀이 마르며 몸을 데우는 일은 없고, 일로 쓴 에너지가 몸을 데우지도 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ΔS = (M − W) ± R ± C − E&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;신체의 열교환&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「W는 빼기, E 도 빼기, R와 C 만 ±」&lt;/strong&gt;다 — &lt;strong&gt;땀이 마르며 몸을 데우는 일은 없고, 일로 쓴 에너지가 몸을 데우지도 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ΔS = (M − W) ± R ± C − E&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6087,17 +6087,17 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;HSI 는 열압박지수(Heat Stress Index)&lt;/strong&gt;로 소리와 상관없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음량수준의 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000Hz 순음과 같게 들리는 음압수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 phon 을 1 sone 으로 삼은 상대적 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;10 phon 오를 때마다 2배&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PLdB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감각소음수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3,150Hz 기준&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;HSI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열압박지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;온열환경의 척도&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;HSI는 열압박지수(Heat Stress Index)&lt;/strong&gt;로 소리와 상관없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음량수준의 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000Hz 순음과 같게 들리는 음압수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 phon을 1 sone으로 삼은 상대적 크기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;10 phon 오를 때마다 2배&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PLdB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감각소음수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;3,150Hz 기준&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;HSI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열압박지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;온열환경의 척도&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>① phon 은 음량수준의 척도다.&lt;br&gt;③ PLdB 도 그렇다.&lt;br&gt;④ sone 도 그렇다.</t>
+          <t>① phon은 음량수준의 척도다.&lt;br&gt;③ PLdB 도 그렇다.&lt;br&gt;④ sone 도 그렇다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;음량수준의 척도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;셋 다 소리 이름이 붙어 있는데 하나만 「H(Heat) · S(Stress)」&lt;/strong&gt;다 — &lt;strong&gt;열에 관한 낱말&lt;/strong&gt;이라 결이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;HSI 는 열압박지수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;음량수준의 척도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;셋 다 소리 이름이 붙어 있는데 하나만 「H(Heat) · S(Stress)」&lt;/strong&gt;다 — &lt;strong&gt;열에 관한 낱말&lt;/strong&gt;이라 결이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;HSI는 열압박지수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6345,17 +6345,17 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;낮은 주파수에 큰 강도&lt;/strong&gt;를 지닌 음에서 JND 가 가장 작다. &lt;strong&gt;작은 변화도 알아챈다&lt;/strong&gt;는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;변화감지역(JND)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차이를 알아챌 수 있는 가장 작은 변화량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작을수록&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예민하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작은 차이도 가려낸다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주파수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 ~ 2,000Hz 이하의 낮은 쪽에서 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;강도가 클수록 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;따라서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮은 주파수 + 큰 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;낮은 주파수에 큰 강도&lt;/strong&gt;를 지닌 음에서 JND가 가장 작다. &lt;strong&gt;작은 변화도 알아챈다&lt;/strong&gt;는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;변화감지역(JND)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차이를 알아챌 수 있는 가장 작은 변화량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작을수록&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예민하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작은 차이도 가려낸다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주파수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 ~ 2,000Hz 이하의 낮은 쪽에서 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;강도가 클수록 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;따라서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮은 주파수 + 큰 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
         <is>
-          <t>① 낮은 주파수라도 강도가 작으면 JND 가 커진다.&lt;br&gt;③ 높은 주파수에 작은 강도면 가장 둔하다.&lt;br&gt;④ 높은 주파수에 큰 강도여도 낮은 주파수만 못하다.</t>
+          <t>① 낮은 주파수라도 강도가 작으면 JND가 커진다.&lt;br&gt;③ 높은 주파수에 작은 강도면 가장 둔하다.&lt;br&gt;④ 높은 주파수에 큰 강도여도 낮은 주파수만 못하다.</t>
         </is>
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;변화감지역(JND)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;JND 가 작다 = 예민하다&lt;/strong&gt;는 것부터 잡는다 — &lt;strong&gt;크고 또렷한 소리(큰 강도)일수록, 귀가 잘 듣는 낮은 대역일수록&lt;/strong&gt; 작은 차이를 가려낸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;낮은 주파수 · 큰 강도에서 JND 가 가장 작다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;변화감지역(JND)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;JND가 작다 = 예민하다&lt;/strong&gt;는 것부터 잡는다 — &lt;strong&gt;크고 또렷한 소리(큰 강도)일수록, 귀가 잘 듣는 낮은 대역일수록&lt;/strong&gt; 작은 차이를 가려낸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;낮은 주파수 · 큰 강도에서 JND가 가장 작다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
       <c r="W44" s="32" t="inlineStr"/>
       <c r="X44" s="32" t="inlineStr">
         <is>
-          <t>탁상용 연삭기에서 숫돌과 작업 받침대의 간격이 5mm 이다.</t>
+          <t>탁상용 연삭기에서 숫돌과 작업 받침대의 간격이 5mm이다.</t>
         </is>
       </c>
       <c r="Y44" s="32" t="inlineStr"/>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="AH46" s="32" t="inlineStr">
         <is>
-          <t>① Fail Safe 는 기계 고장에 대비한 설계다.&lt;br&gt;② 다중계화는 같은 기능을 여럿 두는 것이다.&lt;br&gt;④ Back up 은 예비계통을 두는 것이다.</t>
+          <t>① Fail Safe는 기계 고장에 대비한 설계다.&lt;br&gt;② 다중계화는 같은 기능을 여럿 두는 것이다.&lt;br&gt;④ Back up은 예비계통을 두는 것이다.</t>
         </is>
       </c>
       <c r="AI46" s="32" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="AH49" s="32" t="inlineStr">
         <is>
-          <t>① 140mm 는 계산과 맞지 않는다.&lt;br&gt;② 200mm 도 그렇다.&lt;br&gt;③ 260mm 도 그렇다.</t>
+          <t>① 140mm는 계산과 맞지 않는다.&lt;br&gt;② 200mm 도 그렇다.&lt;br&gt;③ 260mm 도 그렇다.</t>
         </is>
       </c>
       <c r="AI49" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;프레스 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1,600 이라는 수는 사람 손이 초당 1,600mm 로 들어온다&lt;/strong&gt;는 가정이다 — &lt;strong&gt;멈추는 데 걸린 시간(초)에 곱하면 그동안 손이 들어올 거리&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전거리 = 1,600 × 정지시간(초)&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;프레스 방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1,600이라는 수는 사람 손이 초당 1,600mm로 들어온다&lt;/strong&gt;는 가정이다 — &lt;strong&gt;멈추는 데 걸린 시간(초)에 곱하면 그동안 손이 들어올 거리&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;안전거리 = 1,600 × 정지시간(초)&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7898,12 @@
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
-          <t>② fail-passive 의 설명은 옳다.&lt;br&gt;③ fail-active 의 설명도 옳다.&lt;br&gt;④ fail-operational 의 설명도 옳다.</t>
+          <t>② fail-passive의 설명은 옳다.&lt;br&gt;③ fail-active의 설명도 옳다.&lt;br&gt;④ fail-operational의 설명도 옳다.</t>
         </is>
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;페일 세이프의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;①의 「인간이 취급을 잘못해도」라는 대목이 곧 풀 프루프&lt;/strong&gt;다 — &lt;strong&gt;나머지 셋은 모두 「부품이 고장 나면」으로 시작&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람의 실수에 대비하는 것은 풀 프루프&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;페일 세이프의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;①의 「인간이 취급을 잘못해도」라는 대목이 곧 풀 프루프&lt;/strong&gt;다 — &lt;strong&gt;나머지 셋은 모두 「부품이 고장 나면」으로 시작&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람의 실수에 대비하는 것은 풀 프루프&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="AG57" s="32" t="inlineStr">
         <is>
-          <t>화기를 사용하는 설비로부터 &lt;strong&gt;3m 를 초과&lt;/strong&gt; 하는 장소다. &lt;strong&gt;「1m」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;아세틸렌 용접장치의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;게이지 압력 127kPa 초과 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1.3 kgf/cm²&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생기실의 위치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건물의 최상층 · 화기 사용 설비에서 3m 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「1m」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외 설치 시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개구부를 다른 건축물로부터 1.5m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생기실의 벽&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불연성 재료 · 철근콘크리트 이상의 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지붕과 천장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얇은 철판이나 가벼운 불연성 재료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>화기를 사용하는 설비로부터 &lt;strong&gt;3m를 초과&lt;/strong&gt;하는 장소다. &lt;strong&gt;「1m」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;아세틸렌 용접장치의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;게이지 압력 127kPa 초과 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1.3 kgf/cm²&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생기실의 위치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;건물의 최상층 · 화기 사용 설비에서 3m 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「1m」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외 설치 시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개구부를 다른 건축물로부터 1.5m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생기실의 벽&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불연성 재료 · 철근콘크리트 이상의 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지붕과 천장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;얇은 철판이나 가벼운 불연성 재료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH57" s="32" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AG58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;회전축 중량 1톤 초과 + 원주속도 초당 120m 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고속회전체의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고속회전체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원주속도가 초당 25m 를 넘는 회전체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비파괴검사 대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;회전축 중량 1톤 초과 + 원주속도 초당 120m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;회전시험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전용 운전실 밖에서 원격조작&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;회전축 중량 1톤 초과 + 원주속도 초당 120m 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고속회전체의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고속회전체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;원주속도가 초당 25m를 넘는 회전체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비파괴검사 대상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;회전축 중량 1톤 초과 + 원주속도 초당 120m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;회전시험&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전용 운전실 밖에서 원격조작&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH58" s="32" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>② 30cm 는 기준값이 아니다.&lt;br&gt;③ 35cm 도 그렇다.&lt;br&gt;④ 40cm 도 그렇다.</t>
+          <t>② 30cm는 기준값이 아니다.&lt;br&gt;③ 35cm 도 그렇다.&lt;br&gt;④ 40cm 도 그렇다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AI60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;구내운반차의 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;65cm 는 「팔을 벌려 핸들을 잡아도 차체 밖으로 손이 나가지 않을」 거리&lt;/strong&gt;다 — &lt;strong&gt;70 으로 반듯하게 바꿔 놓은 보기&lt;/strong&gt;가 틀렸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;핸들 중심에서 차체 바깥까지 65cm 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;구내운반차의 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;65cm는 「팔을 벌려 핸들을 잡아도 차체 밖으로 손이 나가지 않을」 거리&lt;/strong&gt;다 — &lt;strong&gt;70으로 반듯하게 바꿔 놓은 보기&lt;/strong&gt;가 틀렸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;핸들 중심에서 차체 바깥까지 65cm 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="AI61" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;롤러기의 급정지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;배꼽 높이는 1m 안팎&lt;/strong&gt;이다 — &lt;strong&gt;1.2 ~ 1.4m 는 가슴에서 어깨&lt;/strong&gt;라 배로 누를 수 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;복부 조작식은 0.8 ~ 1.1m&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;롤러기의 급정지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;배꼽 높이는 1m 안팎&lt;/strong&gt;이다 — &lt;strong&gt;1.2 ~ 1.4m는 가슴에서 어깨&lt;/strong&gt;라 배로 누를 수 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;복부 조작식은 0.8 ~ 1.1m&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9054,12 +9054,12 @@
       </c>
       <c r="AG62" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수조작식&lt;/strong&gt;은 &lt;strong&gt;손이 금형에 들어가는 것을 전제&lt;/strong&gt;로 한 hand in die 방식이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;No hand in die 와 Hand in die&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전금형 · 안전울(방호울) · 전용프레스 · 자동송급장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①③④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가드식 · 수인식 · 손쳐내기식 · 양수조작식 · 광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;양수조작식&lt;/strong&gt;은 &lt;strong&gt;손이 금형에 들어가는 것을 전제&lt;/strong&gt;로 한 hand in die 방식이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;No hand in die와 Hand in die&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;방식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전금형 · 안전울(방호울) · 전용프레스 · 자동송급장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①③④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Hand in die&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가드식 · 수인식 · 손쳐내기식 · 양수조작식 · 광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH62" s="32" t="inlineStr">
         <is>
-          <t>① 안전금형을 부착한 프레스는 No hand in die 다.&lt;br&gt;③ 안전울을 부착한 프레스도 그렇다.&lt;br&gt;④ 전용프레스의 도입도 그렇다.</t>
+          <t>① 안전금형을 부착한 프레스는 No hand in die다.&lt;br&gt;③ 안전울을 부착한 프레스도 그렇다.&lt;br&gt;④ 전용프레스의 도입도 그렇다.</t>
         </is>
       </c>
       <c r="AI62" s="32" t="inlineStr">
@@ -9317,12 +9317,12 @@
       </c>
       <c r="AH64" s="32" t="inlineStr">
         <is>
-          <t>① 12 J 은 계산과 맞지 않는다.&lt;br&gt;③ 32 J 도 그렇다.&lt;br&gt;④ 42 J 도 그렇다.</t>
+          <t>① 12 J은 계산과 맞지 않는다.&lt;br&gt;③ 32 J 도 그렇다.&lt;br&gt;④ 42 J 도 그렇다.</t>
         </is>
       </c>
       <c r="AI64" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험한계에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;500Ω 일 때 13.6 J&lt;/strong&gt;을 기준 삼으면 &lt;strong&gt;800Ω 은 그 1.6배인 21.8 J&lt;/strong&gt;로 곧장 나온다 — &lt;strong&gt;저항만 바꿔 되풀이 출제&lt;/strong&gt; 되는 문항이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;800Ω 이면 약 22 J&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험한계에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;500Ω 일 때 13.6 J&lt;/strong&gt;을 기준 삼으면 &lt;strong&gt;800Ω 은 그 1.6배인 21.8 J&lt;/strong&gt;로 곧장 나온다 — &lt;strong&gt;저항만 바꿔 되풀이 출제&lt;/strong&gt;되는 문항이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;800Ω 이면 약 22 J&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="U66" s="32" t="inlineStr">
         <is>
-          <t>지락사고 시 1초를 초과하고 2초 이내에 고압전로를 자동차단하는 장치가 설치되어 있는 고압전로에 제2종 접지공사를 하였다. 접지저항은 몇 Ω이하로 유지해야 하는가? (단, 변압기의 고압측 전로의 1선 지락전류는 10A 이다.)</t>
+          <t>지락사고 시 1초를 초과하고 2초 이내에 고압전로를 자동차단하는 장치가 설치되어 있는 고압전로에 제2종 접지공사를 하였다. 접지저항은 몇 Ω이하로 유지해야 하는가? (단, 변압기의 고압측 전로의 1선 지락전류는 10A이다.)</t>
         </is>
       </c>
       <c r="V66" s="32" t="inlineStr"/>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;변압기 중성점 접지저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;빨리 끊을수록 저항을 크게 허용&lt;/strong&gt; 한다 — &lt;strong&gt;150 → 300 → 600&lt;/strong&gt;으로 두 배씩 커진다. &lt;strong&gt;위험한 시간이 짧으니 조건을 늦춰 주는 것&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1초 초과 2초 이내는 300 ÷ 1선지락전류&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 한국전기설비규정(KEC)은 「제1종·제2종 접지공사」라는 종별 구분을 없애고 계통접지(TN·TT·IT)와 보호도체 방식으로 바꾸었다. 이 문항은 개정 전 기준으로 출제되어 ③이 정답으로 처리되었다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;변압기 중성점 접지저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;빨리 끊을수록 저항을 크게 허용&lt;/strong&gt;한다 — &lt;strong&gt;150 → 300 → 600&lt;/strong&gt;으로 두 배씩 커진다. &lt;strong&gt;위험한 시간이 짧으니 조건을 늦춰 주는 것&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1초 초과 2초 이내는 300 ÷ 1선지락전류&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 한국전기설비규정(KEC)은 「제1종·제2종 접지공사」라는 종별 구분을 없애고 계통접지(TN·TT·IT)와 보호도체 방식으로 바꾸었다. 이 문항은 개정 전 기준으로 출제되어 ③이 정답으로 처리되었다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9699,17 +9699,17 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>가스의 발화점이 &lt;strong&gt;120℃&lt;/strong&gt;이므로 &lt;strong&gt;기기의 최고표면온도가 그보다 낮은 T5(100℃ 이하)&lt;/strong&gt; 라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭기기의 온도등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;450℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120℃ 보다 높다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>가스의 발화점이 &lt;strong&gt;120℃&lt;/strong&gt;이므로 &lt;strong&gt;기기의 최고표면온도가 그보다 낮은 T5(100℃ 이하)&lt;/strong&gt;라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭기기의 온도등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;450℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120℃ 보다 높다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85℃ 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>① T2 는 300℃ 이하로 발화점보다 높다.&lt;br&gt;② T3 는 200℃ 이하로 역시 높다.&lt;br&gt;③ T4 는 135℃ 이하로 120℃ 보다 높다.</t>
+          <t>① T2는 300℃ 이하로 발화점보다 높다.&lt;br&gt;② T3는 200℃ 이하로 역시 높다.&lt;br&gt;③ T4는 135℃ 이하로 120℃ 보다 높다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방폭기기의 온도등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기기 표면이 가스의 발화점보다 낮아야&lt;/strong&gt; 불이 안 붙는다 — &lt;strong&gt;135℃(T4)는 120℃ 를 넘으니 안 되고, 100℃(T5)라야&lt;/strong&gt; 한다. &lt;strong&gt;450 · 300 · 200 · 135 · 100 · 85&lt;/strong&gt; 여섯 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;T4 는 135℃, T5 는 100℃ 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방폭기기의 온도등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기기 표면이 가스의 발화점보다 낮아야&lt;/strong&gt; 불이 안 붙는다 — &lt;strong&gt;135℃(T4)는 120℃ 를 넘으니 안 되고, 100℃(T5)라야&lt;/strong&gt; 한다. &lt;strong&gt;450 · 300 · 200 · 135 · 100 · 85&lt;/strong&gt; 여섯 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;T4는 135℃, T5는 100℃ 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="AH68" s="32" t="inlineStr">
         <is>
-          <t>② 35 ~ 50V 는 여전히 위험한 수준이다.&lt;br&gt;③ 55 ~ 75V 는 평상시 무부하 전압에 가깝다.&lt;br&gt;④ 80 ~ 100V 는 더 높다.</t>
+          <t>② 35 ~ 50V는 여전히 위험한 수준이다.&lt;br&gt;③ 55 ~ 75V는 평상시 무부하 전압에 가깝다.&lt;br&gt;④ 80 ~ 100V는 더 높다.</t>
         </is>
       </c>
       <c r="AI68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자동전격방지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;평상시 60 ~ 95V 를 아크가 끊긴 뒤 25 ~ 30V 로&lt;/strong&gt; 떨어뜨린다 — &lt;strong&gt;안전전압(30V) 언저리까지 내리는 것&lt;/strong&gt;이 목적이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아크 중단 후 25 ~ 30V 이하, 1초 이내&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자동전격방지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;평상시 60 ~ 95V를 아크가 끊긴 뒤 25 ~ 30V로&lt;/strong&gt; 떨어뜨린다 — &lt;strong&gt;안전전압(30V) 언저리까지 내리는 것&lt;/strong&gt;이 목적이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아크 중단 후 25 ~ 30V 이하, 1초 이내&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 33.33% 는 분모를 충격절연강도로 잡은 값에 가깝다.&lt;br&gt;② 47.33% 는 계산과 맞지 않는다.&lt;br&gt;④ 63.5% 도 그렇다.</t>
+          <t>① 33.33%는 분모를 충격절연강도로 잡은 값에 가깝다.&lt;br&gt;② 47.33%는 계산과 맞지 않는다.&lt;br&gt;④ 63.5% 도 그렇다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
@@ -10470,12 +10470,12 @@
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
-          <t>① ib 는 1종 장소에도 쓸 수 있다.&lt;br&gt;② p(압력 방폭구조)도 1종 장소에 쓸 수 있다.&lt;br&gt;③ e(안전증 방폭구조)도 그렇다.</t>
+          <t>① ib는 1종 장소에도 쓸 수 있다.&lt;br&gt;② p(압력 방폭구조)도 1종 장소에 쓸 수 있다.&lt;br&gt;③ e(안전증 방폭구조)도 그렇다.</t>
         </is>
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방폭구조의 기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물음이 「정상에서는 없고 이상 시에만 잠깐」&lt;/strong&gt;이라 했으니 &lt;strong&gt;2종 장소&lt;/strong&gt;다 — &lt;strong&gt;2종에만 쓰는 것은 n 하나&lt;/strong&gt; 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;2종 장소 전용은 n(비점화 방폭구조)&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방폭구조의 기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물음이 「정상에서는 없고 이상 시에만 잠깐」&lt;/strong&gt;이라 했으니 &lt;strong&gt;2종 장소&lt;/strong&gt;다 — &lt;strong&gt;2종에만 쓰는 것은 n 하나&lt;/strong&gt;뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;2종 장소 전용은 n(비점화 방폭구조)&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10991,7 +10991,7 @@
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전압이 높을수록 더 큰 절연저항&lt;/strong&gt;을 요구한다 — &lt;strong&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/strong&gt;로 차례로 오른다. &lt;strong&gt;220V 는 두 번째 칸&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;220V 는 0.2MΩ 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 한국전기설비규정(KEC)은 전로의 사용전압에 따라 SELV·PELV 0.5MΩ, FELV·500V 이하 1.0MΩ, 500V 초과 1.0MΩ 이상으로 정하고 있다. 이 문항은 개정 전 기준으로 출제되어 ②가 정답으로 처리되었다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전압이 높을수록 더 큰 절연저항&lt;/strong&gt;을 요구한다 — &lt;strong&gt;0.1 · 0.2 · 0.3 · 0.4&lt;/strong&gt;로 차례로 오른다. &lt;strong&gt;220V는 두 번째 칸&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;220V는 0.2MΩ 이상&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 한국전기설비규정(KEC)은 전로의 사용전압에 따라 SELV·PELV 0.5MΩ, FELV·500V 이하 1.0MΩ, 500V 초과 1.0MΩ 이상으로 정하고 있다. 이 문항은 개정 전 기준으로 출제되어 ②가 정답으로 처리되었다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="AI80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전기안전의 일반사항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「전선 접속 시 세기 20% 이상 감소 금지」&lt;/strong&gt;는 자주 나오는 값이다 — &lt;strong&gt;30% 로 늘려 놓은 보기&lt;/strong&gt;가 오답이다. &lt;strong&gt;피뢰침과 누전은 아예 다른 이야기&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전선 접속 시 세기는 20% 이상 줄지 않게&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 한국전기설비규정(KEC)은 「제3종·특별 제3종 접지공사」라는 종별 구분을 없앴다. 이 문항은 개정 전 기준으로 출제되어 ②가 정답으로 처리되었다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전기안전의 일반사항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「전선 접속 시 세기 20% 이상 감소 금지」&lt;/strong&gt;는 자주 나오는 값이다 — &lt;strong&gt;30%로 늘려 놓은 보기&lt;/strong&gt;가 오답이다. &lt;strong&gt;피뢰침과 누전은 아예 다른 이야기&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전선 접속 시 세기는 20% 이상 줄지 않게&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 한국전기설비규정(KEC)은 「제3종·특별 제3종 접지공사」라는 종별 구분을 없앴다. 이 문항은 개정 전 기준으로 출제되어 ②가 정답으로 처리되었다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지하작업장의 가스 측정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;8시간이면 하루 일과가 다 끝난 뒤&lt;/strong&gt;라 뜻이 없다 — &lt;strong&gt;오전·오후로 나눈 4시간&lt;/strong&gt; 이라야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;장시간 작업은 4시간마다 측정&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지하작업장의 가스 측정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;8시간이면 하루 일과가 다 끝난 뒤&lt;/strong&gt;라 뜻이 없다 — &lt;strong&gt;오전·오후로 나눈 4시간&lt;/strong&gt;이라야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;장시간 작업은 4시간마다 측정&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12002,12 +12002,12 @@
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>① Flame arrester 는 화염의 전파를 막는 장치다.&lt;br&gt;② Vent stack 은 압력을 대기로 내보내는 설비다.&lt;br&gt;③ 긴급방출장치는 내용물을 빼내는 설비다.</t>
+          <t>① Flame arrester는 화염의 전파를 막는 장치다.&lt;br&gt;② Vent stack은 압력을 대기로 내보내는 설비다.&lt;br&gt;③ 긴급방출장치는 내용물을 빼내는 설비다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방유제&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물음이 「누출되어 확산되는 것을 방지」&lt;/strong&gt; 라고 했다 — &lt;strong&gt;퍼지지 못하게 가두는 것은 둑(제방)&lt;/strong&gt; 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;인화성 액체 저장탱크에는 방유제&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방유제&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물음이 「누출되어 확산되는 것을 방지」&lt;/strong&gt; 라고 했다 — &lt;strong&gt;퍼지지 못하게 가두는 것은 둑(제방)&lt;/strong&gt;뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;인화성 액체 저장탱크에는 방유제&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="AG88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;플라스틱 원료&lt;/strong&gt;는 &lt;strong&gt;제외 대상이 아니라 MSDS 를 작성·비치해야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MSDS 작성·비치 제외 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;제외 대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건강기능식품 · 식품 및 식품첨가물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;농약 · 비료 · 사료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화장품 · 의약품 및 의약외품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방사성물질 · 원료물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폐기물 · 화약류 · 마약 및 향정신성의약품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 화학물질(플라스틱 원료 등)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제외 대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;플라스틱 원료&lt;/strong&gt;는 &lt;strong&gt;제외 대상이 아니라 MSDS를 작성·비치해야&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MSDS 작성·비치 제외 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;제외 대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건강기능식품 · 식품 및 식품첨가물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;농약 · 비료 · 사료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화장품 · 의약품 및 의약외품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방사성물질 · 원료물질&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폐기물 · 화약류 · 마약 및 향정신성의약품&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 화학물질(플라스틱 원료 등)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제외 대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH88" s="32" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;MSDS 의 작성·비치 제외 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;제외되는 것은 「다른 법으로 이미 관리되는 것」&lt;/strong&gt;이다 — &lt;strong&gt;식품 · 농약 · 화장품 · 의약품 · 방사성물질&lt;/strong&gt;이 그렇다. &lt;strong&gt;플라스틱 원료는 그런 별도 법이 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플라스틱 원료는 MSDS 대상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;MSDS의 작성·비치 제외 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;제외되는 것은 「다른 법으로 이미 관리되는 것」&lt;/strong&gt;이다 — &lt;strong&gt;식품 · 농약 · 화장품 · 의약품 · 방사성물질&lt;/strong&gt;이 그렇다. &lt;strong&gt;플라스틱 원료는 그런 별도 법이 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;플라스틱 원료는 MSDS 대상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13124,7 +13124,7 @@
       </c>
       <c r="U94" s="32" t="inlineStr">
         <is>
-          <t>다음 중 최소발화에너지(E[J])를 구하는 식으로 옳은 것은? (단, I는 전류[A]. R 은 저항[Ω], V는 전압[V], C는 콘덴서 용량[F], T는 시간[초]이라 한다.)</t>
+          <t>다음 중 최소발화에너지(E[J])를 구하는 식으로 옳은 것은? (단, I는 전류[A]. R은 저항[Ω], V는 전압[V], C는 콘덴서 용량[F], T는 시간[초]이라 한다.)</t>
         </is>
       </c>
       <c r="V94" s="32" t="inlineStr"/>
@@ -13163,7 +13163,7 @@
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>① E=I²RT 는 줄열의 식이다.&lt;br&gt;② E=0.24I²RT 는 줄열을 칼로리로 나타낸 식이다.&lt;br&gt;④ E = ½√(CV) 는 물리적 뜻이 없는 꼴이다.</t>
+          <t>① E=I²RT는 줄열의 식이다.&lt;br&gt;② E=0.24I²RT는 줄열을 칼로리로 나타낸 식이다.&lt;br&gt;④ E = ½√(CV)는 물리적 뜻이 없는 꼴이다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="AH96" s="32" t="inlineStr">
         <is>
-          <t>① 하론 1031 은 F 가 없고 Cl 이 셋이라는 뜻이다.&lt;br&gt;② 하론 1211 은 CF₂ClBr 이다.&lt;br&gt;④ 하론 2402 는 C₂F₄Br₂ 다.</t>
+          <t>① 하론 1031은 F가 없고 Cl이 셋이라는 뜻이다.&lt;br&gt;② 하론 1211은 CF₂ClBr이다.&lt;br&gt;④ 하론 2402는 C₂F₄Br₂ 다.</t>
         </is>
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;할론 번호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「탄 · 불 · 염 · 브」&lt;/strong&gt; 순으로 개수를 적는다 — &lt;strong&gt;CF₃Br 은 1 · 3 · 0 · 1&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CF₃Br 은 하론 1301&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;할론 번호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「탄 · 불 · 염 · 브」&lt;/strong&gt; 순으로 개수를 적는다 — &lt;strong&gt;CF₃Br은 1 · 3 · 0 · 1&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CF₃Br은 하론 1301&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>② flame arrester 는 화염의 전파를 막는 장치다.&lt;br&gt;③ seal drum 은 물로 봉수하는 장치다.&lt;br&gt;④ purge 는 치환하는 조작이지 장치가 아니다.</t>
+          <t>② flame arrester는 화염의 전파를 막는 장치다.&lt;br&gt;③ seal drum은 물로 봉수하는 장치다.&lt;br&gt;④ purge는 치환하는 조작이지 장치가 아니다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>② 6m 는 기준값이 아니다.&lt;br&gt;③ 5m 도 그렇다.&lt;br&gt;④ 4m 도 그렇다.</t>
+          <t>② 6m는 기준값이 아니다.&lt;br&gt;③ 5m 도 그렇다.&lt;br&gt;④ 4m 도 그렇다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14590,7 +14590,7 @@
       </c>
       <c r="AH105" s="32" t="inlineStr">
         <is>
-          <t>① 전체길이의 4분의 1 은 기준값이 아니다.&lt;br&gt;③ 전체길이의 3분의 2 도 그렇다.&lt;br&gt;④ 전체길이의 2분의 1 도 그렇다.</t>
+          <t>① 전체길이의 4분의 1은 기준값이 아니다.&lt;br&gt;③ 전체길이의 3분의 2 도 그렇다.&lt;br&gt;④ 전체길이의 2분의 1 도 그렇다.</t>
         </is>
       </c>
       <c r="AI105" s="32" t="inlineStr">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="AI107" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;건물 해체용 기구&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;해체는 「부수고 · 자르고 · 밀어내는」 일&lt;/strong&gt;이다 — &lt;strong&gt;스크레이퍼는 흙을 긁어 담아 나르는 기계&lt;/strong&gt;라 결이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;스크레이퍼는 해체용 기구가 아니다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;건물 해체용 기구&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;해체는 「부수고 · 자르고 · 밀어내는」일&lt;/strong&gt;이다 — &lt;strong&gt;스크레이퍼는 흙을 긁어 담아 나르는 기계&lt;/strong&gt;라 결이 다르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;스크레이퍼는 해체용 기구가 아니다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="AG111" s="32" t="inlineStr">
         <is>
-          <t>버팀줄은 &lt;strong&gt;3개 이상&lt;/strong&gt; 이라야 한다. &lt;strong&gt;「2개」로는 한 방향으로 넘어간다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;항타기ㆍ항발기의 무너짐 방지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연약한 지반에는 깔판·깔목 등으로 침하를 막는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;미끄러질 우려가 있으면 말뚝이나 쐐기로 고정한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀대만으로 안정시킬 때는 버팀대 3개 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀줄만으로 안정시킬 때는 버팀줄 3개 이상, 같은 간격으로 배치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「2개」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시설이나 가설물에 고정할 때는 그 하중을 견딜 수 있는 것으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>버팀줄은 &lt;strong&gt;3개 이상&lt;/strong&gt;이라야 한다. &lt;strong&gt;「2개」로는 한 방향으로 넘어간다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;항타기ㆍ항발기의 무너짐 방지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연약한 지반에는 깔판·깔목 등으로 침하를 막는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;미끄러질 우려가 있으면 말뚝이나 쐐기로 고정한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀대만으로 안정시킬 때는 버팀대 3개 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀줄만으로 안정시킬 때는 버팀줄 3개 이상, 같은 간격으로 배치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「2개」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시설이나 가설물에 고정할 때는 그 하중을 견딜 수 있는 것으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH111" s="32" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="AG113" s="32" t="inlineStr">
         <is>
-          <t>달줄·달포대는 &lt;strong&gt;쓰게 해야&lt;/strong&gt; 한다. &lt;strong&gt;던져 올리고 내리면 위험&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;거푸집동바리 조립·해체 시 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계 근로자가 아닌 사람의 출입을 금지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비·눈 등으로 날씨가 몹시 나쁘면 작업을 중지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재료·기구·공구를 올리거나 내릴 때는 달줄·달포대를 쓰게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「금하도록」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀목을 설치하고 인양장비에 매단 뒤 작업한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>달줄·달포대는 &lt;strong&gt;쓰게 해야&lt;/strong&gt; 한다. &lt;strong&gt;던져 올리고 내리면 위험&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;거푸집동바리 조립·해체 시 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계 근로자가 아닌 사람의 출입을 금지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비·눈 등으로 날씨가 몹시 나쁘면 작업을 중지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재료·기구·공구를 올리거나 내릴 때는 달줄·달포대를 쓰게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「금하도록」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀목을 설치하고 인양장비에 매단 뒤 작업한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH113" s="32" t="inlineStr">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="AI114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;구조물 해체공법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;해체는 「눌러 부수고 · 밀어 넘기고 · 잘라내고 · 터뜨리는」 일&lt;/strong&gt;이다 — &lt;strong&gt;「진공」으로는 구조물을 무너뜨릴 수 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;진공공법은 해체공법이 아니다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;구조물 해체공법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;해체는 「눌러 부수고 · 밀어 넘기고 · 잘라내고 · 터뜨리는」일&lt;/strong&gt;이다 — &lt;strong&gt;「진공」으로는 구조물을 무너뜨릴 수 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;진공공법은 해체공법이 아니다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16009,7 +16009,7 @@
       </c>
       <c r="AH116" s="32" t="inlineStr">
         <is>
-          <t>② 15,060N 은 계산과 맞지 않는다.&lt;br&gt;③ 16,060N 도 그렇다.&lt;br&gt;④ 17,060N 도 그렇다.</t>
+          <t>② 15,060N은 계산과 맞지 않는다.&lt;br&gt;③ 16,060N 도 그렇다.&lt;br&gt;④ 17,060N 도 그렇다.</t>
         </is>
       </c>
       <c r="AI116" s="32" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="AG117" s="32" t="inlineStr">
         <is>
-          <t>긴 물건은 &lt;strong&gt;앞쪽을 높인다&lt;/strong&gt;. &lt;strong&gt;원통 물건을 굴려 나르는 것도 위험&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인력운반의 안전수칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보조기구를 효과적으로 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;팔과 무릎을 쓰고 척추는 곧게 편다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무거운 물건은 여럿이 함께 든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;긴 물건은 앞쪽을 높게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「뒤쪽」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원통 물건은 굴리지 않고 운반기구를 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>긴 물건은 &lt;strong&gt;앞쪽을 높인다&lt;/strong&gt;. &lt;strong&gt;원통 물건을 굴려 나르는 것도 위험&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인력운반의 안전수칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;수칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보조기구를 효과적으로 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;팔과 무릎을 쓰고 척추는 곧게 편다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무거운 물건은 여럿이 함께 든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;긴 물건은 앞쪽을 높게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「뒤쪽」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원통 물건은 굴리지 않고 운반기구를 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH117" s="32" t="inlineStr">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="AI119" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전락 방지 울타리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90cm 는 안전난간 상부난간대의 아래 한계와 같은 값&lt;/strong&gt;이다 — &lt;strong&gt;사람의 허리 위쯤&lt;/strong&gt;이라 넘어지며 빠지지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;케틀·호퍼·피트의 울타리는 90cm 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전락 방지 울타리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90cm는 안전난간 상부난간대의 아래 한계와 같은 값&lt;/strong&gt;이다 — &lt;strong&gt;사람의 허리 위쯤&lt;/strong&gt;이라 넘어지며 빠지지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;케틀·호퍼·피트의 울타리는 90cm 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="U120" s="32" t="inlineStr">
         <is>
-          <t>안전계수가 4 이고 2000kg/cm2 의 인장강도를 갖는 강선의 최대허용응력은?</t>
+          <t>안전계수가 4이고 2000kg/cm2의 인장강도를 갖는 강선의 최대허용응력은?</t>
         </is>
       </c>
       <c r="V120" s="32" t="inlineStr"/>
@@ -16534,7 +16534,7 @@
       </c>
       <c r="AI120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;허용응력과 안전율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전율이 크면 허용응력은 작아진다&lt;/strong&gt; — &lt;strong&gt;나누는 것&lt;/strong&gt;이라 방향이 뚜렷하다. &lt;strong&gt;2,000 을 그대로 답으로 고르면 안전율을 쓰지 않은 셈&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;허용응력 = 인장강도 ÷ 안전계수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;허용응력과 안전율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전율이 크면 허용응력은 작아진다&lt;/strong&gt; — &lt;strong&gt;나누는 것&lt;/strong&gt;이라 방향이 뚜렷하다. &lt;strong&gt;2,000을 그대로 답으로 고르면 안전율을 쓰지 않은 셈&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;허용응력 = 인장강도 ÷ 안전계수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>

--- a/CBT_2021_3회/산업안전기사_2021_3회_문항등록.xlsx
+++ b/CBT_2021_3회/산업안전기사_2021_3회_문항등록.xlsx
@@ -8606,12 +8606,12 @@
       </c>
       <c r="N59" s="32" t="inlineStr">
         <is>
-          <t>크레인의 권과방지장치</t>
+          <t>와이어로프 등 달기구의 안전계수</t>
         </is>
       </c>
       <c r="O59" s="32" t="inlineStr">
         <is>
-          <t>권과방지장치</t>
+          <t>와이어로프 안전계수</t>
         </is>
       </c>
       <c r="P59" s="32" t="n">
@@ -8628,56 +8628,56 @@
       <c r="S59" s="32" t="inlineStr"/>
       <c r="T59" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2015.03.08 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
+          <t>원본 시행일 2011.03.20 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
         </is>
       </c>
       <c r="U59" s="32" t="inlineStr">
         <is>
-          <t>크레인에서 권과방지장치 달기구 윗면이 권상장치의 아랫면과 접촉할 우려가 있는 경우에는 몇 cm 이상 간격이 되도록 조정하여야 하는가? (단, 작동식 권과장치의 경우는 제외한다.)</t>
+          <t>양중기에서 화물의 하중을 직접 지지하는 와이어로프의 안 전율(계수)은 얼마 이상으로 하는가?</t>
         </is>
       </c>
       <c r="V59" s="32" t="inlineStr"/>
       <c r="W59" s="32" t="inlineStr"/>
       <c r="X59" s="32" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y59" s="32" t="inlineStr"/>
       <c r="Z59" s="32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA59" s="32" t="inlineStr"/>
       <c r="AB59" s="32" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC59" s="32" t="inlineStr"/>
       <c r="AD59" s="32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE59" s="32" t="inlineStr"/>
       <c r="AF59" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;0.25m(25cm) 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;크레인의 권과방지장치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.25m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직동식 권과방지장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.05m 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇을 막나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;달기구가 너무 올라가 권상장치에 부딪히는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖의 방호장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과부하방지장치 · 비상정지장치 · 제동장치 · 훅 해지장치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>화물의 하중을 &lt;strong&gt;직접 지지&lt;/strong&gt; 하는 달기와이어로프·달기체인은 &lt;strong&gt;5 이상&lt;/strong&gt;이다. 사람이 타는 운반구를 지지하는 것은 &lt;strong&gt;10 이상&lt;/strong&gt;으로 갑절이다 — &lt;strong&gt;사람이 매달리면 배로 여유를 둔다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;달기구의 안전계수 (규칙 제163조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 지지하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전계수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근로자가 탑승하는 운반구&lt;/u&gt;를 지지하는 달기와이어로프·달기체인&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화물의 하중을 직접 지지&lt;/u&gt; 하는 달기와이어로프·달기체인&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;훅 · 샤클 · 클램프 · 리프팅 빔&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;그 밖의 경우&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>② 30cm는 기준값이 아니다.&lt;br&gt;③ 35cm 도 그렇다.&lt;br&gt;④ 40cm 도 그렇다.</t>
+          <t>① 3은 훅·샤클·클램프·리프팅 빔의 값이다.&lt;br&gt;③ 7은 규칙에 없는 값이다.&lt;br&gt;④ 9는 규칙에 없는 값이다 — 사람이 타면 9가 아니라 10이다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;크레인의 권과방지장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;일반은 0.25m, 직동식은 0.05m&lt;/strong&gt;로 다섯 배 차이다 — &lt;strong&gt;직동식은 훨씬 정확하게 멈추므로 여유가 적어도 된다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;권과방지장치 간격은 0.25m 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;산업안전보건기준에 관한 규칙 제163조 — 와이어로프 등 달기구의 안전계수&lt;/strong&gt;&lt;br&gt;안전계수는 &lt;strong&gt;끊어지는 힘 ÷ 걸리는 힘&lt;/strong&gt;이다. 값이 클수록 여유가 크다. &lt;strong&gt;사람이 타면 10, 화물만 매달면 5&lt;/strong&gt;로 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;사람 10 · 화물 5 · 훅류 3 · 나머지 4&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C163%EC%A1%B0" target="_blank"&gt;제163조(와이어로프 등 달기구의 안전계수)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;① 사업주는 양중기의 와이어로프 등 달기구의 안전계수(달기구 절단하중의 값을 그 달기구에 걸리는 하중의 최대값으로 나눈 값을 말한다)가 다음 각 호의 구분에 따른 기준에 맞지 아니한 경우에는 이를 사용해서는 아니 된다.&lt;br&gt;▶  1. 근로자가 탑승하는 운반구를 지지하는 달기와이어로프 또는 달기체인의 경우: &lt;strong&gt;10 이상&lt;/strong&gt;&lt;br&gt;▶  2. 화물의 하중을 &lt;strong&gt;직접 지지&lt;/strong&gt;하는 달기와이어로프 또는 달기체인의 경우: 5 이상&lt;br&gt; 3. 훅, 샤클, 클램프, 리프팅 빔의 경우: 3 이상&lt;br&gt; 4. 그 밖의 경우: 4 이상&lt;br&gt;② 사업주는 달기구의 경우 최대허용하중 등의 표식이 견고하게 붙어 있는 것을 사용하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
